--- a/Plots/average_results.xlsx
+++ b/Plots/average_results.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8758064516129032</v>
+        <v>0.8463058183553649</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004017040197077555</v>
+        <v>0.008931327843261399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8756360843189285</v>
+        <v>0.8720839328663378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003996550101957328</v>
+        <v>0.02318794761986417</v>
       </c>
       <c r="G2" t="n">
-        <v>22.18402705515089</v>
+        <v>21.42220618575556</v>
       </c>
       <c r="H2" t="n">
-        <v>0.108347112980168</v>
+        <v>2.201746111821201</v>
       </c>
     </row>
     <row r="3">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8741098677517802</v>
+        <v>0.8458853863632081</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00389538596104697</v>
+        <v>0.003201486021015792</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8739844062024383</v>
+        <v>0.8695998255514302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003776075454863565</v>
+        <v>0.0218453198916433</v>
       </c>
       <c r="G3" t="n">
-        <v>22.28021363173957</v>
+        <v>21.32778107182569</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1013141193074419</v>
+        <v>2.424561132462312</v>
       </c>
     </row>
     <row r="4">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8806338028169014</v>
+        <v>0.7477963697499246</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004632411718246577</v>
+        <v>0.04010031161698811</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8807231679213006</v>
+        <v>0.7871335118966196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004665816329712545</v>
+        <v>0.02874702591219274</v>
       </c>
       <c r="G4" t="n">
-        <v>23.837144339651</v>
+        <v>28.16084181865457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1840530226859428</v>
+        <v>1.530532679221874</v>
       </c>
     </row>
     <row r="5">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8772</v>
+        <v>0.752781746031746</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005254521862167833</v>
+        <v>0.01589977357774736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8775443969011849</v>
+        <v>0.7872744341695569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00518060220485561</v>
+        <v>0.03103278447963139</v>
       </c>
       <c r="G5" t="n">
-        <v>23.44439355165616</v>
+        <v>28.92131158172477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2083238937955884</v>
+        <v>1.209140664408459</v>
       </c>
     </row>
   </sheetData>

--- a/Plots/average_results.xlsx
+++ b/Plots/average_results.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8463058183553649</v>
+        <v>0.4994797086368366</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008931327843261399</v>
+        <v>0.06971904266389178</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8720839328663378</v>
+        <v>0.4716427919735235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02318794761986417</v>
+        <v>0.07744084578198937</v>
       </c>
       <c r="G2" t="n">
-        <v>21.42220618575556</v>
+        <v>24.60535900104058</v>
       </c>
       <c r="H2" t="n">
-        <v>2.201746111821201</v>
+        <v>0.2609261186264291</v>
       </c>
     </row>
     <row r="3">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8458853863632081</v>
+        <v>0.8252797558494405</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003201486021015792</v>
+        <v>0.00330620549338756</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8695998255514302</v>
+        <v>0.8247205196718619</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0218453198916433</v>
+        <v>0.003143894468063013</v>
       </c>
       <c r="G3" t="n">
-        <v>21.32778107182569</v>
+        <v>22.33570701932858</v>
       </c>
       <c r="H3" t="n">
-        <v>2.424561132462312</v>
+        <v>0.08952187182095628</v>
       </c>
     </row>
     <row r="4">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7477963697499246</v>
+        <v>0.5193661971830986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04010031161698811</v>
+        <v>0.05608651911468812</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7871335118966196</v>
+        <v>0.4760050059649277</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02874702591219274</v>
+        <v>0.07686852587826534</v>
       </c>
       <c r="G4" t="n">
-        <v>28.16084181865457</v>
+        <v>34.18700333886422</v>
       </c>
       <c r="H4" t="n">
-        <v>1.530532679221874</v>
+        <v>0.8422452743480875</v>
       </c>
     </row>
     <row r="5">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.752781746031746</v>
+        <v>0.469</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01589977357774736</v>
+        <v>0.04549999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7872744341695569</v>
+        <v>0.3931384240216312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03103278447963139</v>
+        <v>0.06040740825429722</v>
       </c>
       <c r="G5" t="n">
-        <v>28.92131158172477</v>
+        <v>33.88107429590671</v>
       </c>
       <c r="H5" t="n">
-        <v>1.209140664408459</v>
+        <v>2.653960739128324</v>
       </c>
     </row>
   </sheetData>

--- a/Plots/average_results.xlsx
+++ b/Plots/average_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,30 +441,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Average Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Stdev Accuracy</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Average F1-Score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Stdev F1-Score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Average Explainibility</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Stdev Explainibility</t>
         </is>
@@ -481,23 +486,28 @@
           <t>basic</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.4994797086368366</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.06971904266389178</v>
+        <v>0.7549947970863684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4716427919735235</v>
+        <v>0.05739191087828348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07744084578198937</v>
+        <v>0.7549825821450071</v>
       </c>
       <c r="G2" t="n">
-        <v>24.60535900104058</v>
+        <v>0.05828029350704853</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2609261186264291</v>
+        <v>22.41004162330905</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4356160341350464</v>
       </c>
     </row>
     <row r="3">
@@ -508,32 +518,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8252797558494405</v>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.00330620549338756</v>
+        <v>0.7481040892193309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8247205196718619</v>
+        <v>0.06691681119504883</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003143894468063013</v>
+        <v>0.7747888500970325</v>
       </c>
       <c r="G3" t="n">
-        <v>22.33570701932858</v>
+        <v>0.06229432669358891</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08952187182095628</v>
+        <v>18.41524163568774</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5039360285263057</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>amplitude</t>
+          <t>angle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,53 +556,343 @@
           <t>basic</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.5193661971830986</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05608651911468812</v>
+        <v>0.7710571923743501</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4760050059649277</v>
+        <v>0.04181376326089318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07686852587826534</v>
+        <v>0.8559713923083667</v>
       </c>
       <c r="G4" t="n">
-        <v>34.18700333886422</v>
+        <v>0.03064607634900456</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8422452743480875</v>
+        <v>31.72201039861351</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3563809477958694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>angle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7836215666327569</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.04164213175696362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7841411015887589</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04168457354756571</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22.8323499491353</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5370697273583004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7710029069767442</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04753534780029343</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7955628187939032</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04301334998592966</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18.48452034883721</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5683199988154642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.813050847457627</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03743461214875816</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.885613452781507</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02498009478214745</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.97237288135593</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.611524883497826</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>amplitude</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4667002012072435</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.10270979431048</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4230794717452974</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1308939642047191</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31.79621626748133</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.492463159979478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>amplitude</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4612508986340762</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07169145639447902</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3987198709291323</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1171881039692086</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.2236566786407</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.075444165875392</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>amplitude</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4793969849246231</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1906088729949786</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5891231418320155</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1934455418658708</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35.47169708287355</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.191550082023641</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>amplitude</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.04549999999999998</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.3931384240216312</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06040740825429722</v>
-      </c>
-      <c r="G5" t="n">
-        <v>33.88107429590671</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.653960739128324</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4767499999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.05090493590998813</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4417625603840374</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.06042948662608404</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33.14904430791582</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.455412417527903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>amplitude</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03031139409933</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4150999798327438</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0510404201167445</v>
+      </c>
+      <c r="H12" t="n">
+        <v>31.87603355495962</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.279217864551472</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>amplitude</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4913333333333334</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1092087705065649</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6190812471352399</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1024568011527821</v>
+      </c>
+      <c r="H13" t="n">
+        <v>36.12426159157812</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5662268301957</v>
       </c>
     </row>
   </sheetData>

--- a/Plots/average_results.xlsx
+++ b/Plots/average_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,35 +441,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Average Accuracy</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Average Accuracy</t>
+          <t>Stdev Accuracy</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Stdev Accuracy</t>
+          <t>Average F1-Score</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Average F1-Score</t>
+          <t>Stdev F1-Score</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Stdev F1-Score</t>
+          <t>Average Explainibility</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Average Explainibility</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Stdev Explainibility</t>
         </is>
@@ -486,28 +481,23 @@
           <t>basic</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.7501040582726326</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7549947970863684</v>
+        <v>0.05944544564675806</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05739191087828348</v>
+        <v>0.7490371452435526</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7549825821450071</v>
+        <v>0.06043028940269746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05828029350704853</v>
+        <v>22.83069719042664</v>
       </c>
       <c r="H2" t="n">
-        <v>22.41004162330905</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.4356160341350464</v>
+        <v>0.4467662409631784</v>
       </c>
     </row>
     <row r="3">
@@ -518,37 +508,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7679043743641913</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7481040892193309</v>
+        <v>0.05180616503922786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06691681119504883</v>
+        <v>0.7662406787594016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7747888500970325</v>
+        <v>0.05300207974938884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06229432669358891</v>
+        <v>23.0293489318413</v>
       </c>
       <c r="H3" t="n">
-        <v>18.41524163568774</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5039360285263057</v>
+        <v>0.7825938672203077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>angle</t>
+          <t>amplitude</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,34 +541,29 @@
           <t>basic</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0.610261569416499</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7710571923743501</v>
+        <v>0.03855219520701994</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04181376326089318</v>
+        <v>0.6098122277273814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8559713923083667</v>
+        <v>0.04064016785983993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03064607634900456</v>
+        <v>29.38303234638049</v>
       </c>
       <c r="H4" t="n">
-        <v>31.72201039861351</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.3563809477958694</v>
+        <v>1.385540357916369</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>angle</t>
+          <t>amplitude</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,308 +571,23 @@
           <t>strong</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.6024499999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7836215666327569</v>
+        <v>0.02335535270553628</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04164213175696362</v>
+        <v>0.602654074150432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7841411015887589</v>
+        <v>0.02448000238169885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04168457354756571</v>
+        <v>30.43538465281495</v>
       </c>
       <c r="H5" t="n">
-        <v>22.8323499491353</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.5370697273583004</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>angle</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7710029069767442</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.04753534780029343</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.7955628187939032</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.04301334998592966</v>
-      </c>
-      <c r="H6" t="n">
-        <v>18.48452034883721</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5683199988154642</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>angle</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.813050847457627</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.03743461214875816</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.885613452781507</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.02498009478214745</v>
-      </c>
-      <c r="H7" t="n">
-        <v>32.97237288135593</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.611524883497826</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4667002012072435</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.10270979431048</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4230794717452974</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1308939642047191</v>
-      </c>
-      <c r="H8" t="n">
-        <v>31.79621626748133</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.492463159979478</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.4612508986340762</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.07169145639447902</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.3987198709291323</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1171881039692086</v>
-      </c>
-      <c r="H9" t="n">
-        <v>30.2236566786407</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.075444165875392</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.4793969849246231</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1906088729949786</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5891231418320155</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.1934455418658708</v>
-      </c>
-      <c r="H10" t="n">
-        <v>35.47169708287355</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.191550082023641</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4767499999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.05090493590998813</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.4417625603840374</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.06042948662608404</v>
-      </c>
-      <c r="H11" t="n">
-        <v>33.14904430791582</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.455412417527903</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4705</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.03031139409933</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.4150999798327438</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0510404201167445</v>
-      </c>
-      <c r="H12" t="n">
-        <v>31.87603355495962</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.279217864551472</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>amplitude</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4913333333333334</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1092087705065649</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6190812471352399</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.1024568011527821</v>
-      </c>
-      <c r="H13" t="n">
-        <v>36.12426159157812</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.5662268301957</v>
+        <v>1.057907812646517</v>
       </c>
     </row>
   </sheetData>

--- a/Plots/average_results.xlsx
+++ b/Plots/average_results.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8758064516129032</v>
+        <v>0.6679000000000002</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004017040197077555</v>
+        <v>0.03585930841497086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8756360843189285</v>
+        <v>0.6630341479698114</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003996550101957328</v>
+        <v>0.03830933971049442</v>
       </c>
       <c r="G2" t="n">
-        <v>22.18402705515089</v>
+        <v>23.0775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.108347112980168</v>
+        <v>0.09546281998767887</v>
       </c>
     </row>
     <row r="3">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8741098677517802</v>
+        <v>0.6538499999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00389538596104697</v>
+        <v>0.05901357894586635</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8739844062024383</v>
+        <v>0.6505111460659183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003776075454863565</v>
+        <v>0.06151766590838634</v>
       </c>
       <c r="G3" t="n">
-        <v>22.28021363173957</v>
+        <v>22.27735</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1013141193074419</v>
+        <v>0.2179676638861832</v>
       </c>
     </row>
     <row r="4">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8806338028169014</v>
+        <v>0.6416999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004632411718246577</v>
+        <v>0.03760398915008884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8807231679213006</v>
+        <v>0.6464982089188223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004665816329712545</v>
+        <v>0.03737406916697918</v>
       </c>
       <c r="G4" t="n">
-        <v>23.837144339651</v>
+        <v>23.42025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1840530226859428</v>
+        <v>0.8953656027009301</v>
       </c>
     </row>
     <row r="5">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8772</v>
+        <v>0.6579</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005254521862167833</v>
+        <v>0.01468468590062452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8775443969011849</v>
+        <v>0.6598831084693435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00518060220485561</v>
+        <v>0.01725656054771229</v>
       </c>
       <c r="G5" t="n">
-        <v>23.44439355165616</v>
+        <v>27.0107</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2083238937955884</v>
+        <v>1.280891978271391</v>
       </c>
     </row>
   </sheetData>
